--- a/passes.xlsx
+++ b/passes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +745,52 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PP20260707125811</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>07-07-2026</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,322 +477,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PP20260703135810</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>123456</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>bhartesh</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7620096199</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>03-07-2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PP20260703140151</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>123456</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bhartesh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>7620096199</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>03-07-2026</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PP20260703140541</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>123456</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>bhartesh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>7620096199</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>03-07-2026</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PP20260706071419</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sakshi</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>9156396198</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>chakan</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>06-07-2026</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PP20260706072226</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9090</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>9921531890</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>06-07-2026</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PP20260706103234</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7575</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sachin</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>7788639090</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>06-07-2026</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PP20260707125811</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3030</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>vvvvv</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>9874563211</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>vvvv</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
         </is>
       </c>
     </row>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,322 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PP20260703135810</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PP20260703140151</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PP20260703140541</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PP20260706071419</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sakshi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9156396198</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>chakan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP20260706072226</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9090</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9921531890</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PP20260706103234</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7575</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sachin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7788639090</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PP20260707125811</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>07-07-2026</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC7D5A0-94BB-4F34-8F67-F097BCD617EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C016A4-18E7-4BD2-98B6-AFA4AFF45E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22252,12 +22252,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -65828,7 +65831,7 @@
         <v>5877</v>
       </c>
       <c r="D1353" t="s">
-        <v>5228</v>
+        <v>5426</v>
       </c>
       <c r="E1353" s="2" t="s">
         <v>5878</v>
@@ -65839,8 +65842,8 @@
       <c r="G1353" s="2" t="s">
         <v>3273</v>
       </c>
-      <c r="H1353" t="s">
-        <v>3419</v>
+      <c r="H1353" s="3" t="s">
+        <v>3655</v>
       </c>
       <c r="I1353" t="s">
         <v>39</v>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C016A4-18E7-4BD2-98B6-AFA4AFF45E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE515D09-16E1-4758-AA90-D3D12C1FC59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17149" uniqueCount="7392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17156" uniqueCount="7396">
   <si>
     <t>passNumber</t>
   </si>
@@ -22196,13 +22196,25 @@
   </si>
   <si>
     <t>CHAFKAR CHOWK</t>
+  </si>
+  <si>
+    <t>PP20260714001715</t>
+  </si>
+  <si>
+    <t>LAV KUSH BIND</t>
+  </si>
+  <si>
+    <t>CHACKAN CHOWK</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -22215,6 +22227,18 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -22252,7 +22276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -22260,6 +22284,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22563,7 +22591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1716"/>
+  <dimension ref="A1:J1717"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -77468,7 +77496,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1717" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1717" t="s">
+        <v>7392</v>
+      </c>
+      <c r="B1717" s="4">
+        <v>232678</v>
+      </c>
+      <c r="C1717" s="5" t="s">
+        <v>7393</v>
+      </c>
+      <c r="D1717" s="5" t="s">
+        <v>7393</v>
+      </c>
+      <c r="E1717">
+        <v>7080904965</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1717">
+        <v>33</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>7394</v>
+      </c>
+      <c r="I1717" t="s">
+        <v>7395</v>
+      </c>
+      <c r="J1717" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/passes.xlsx
+++ b/passes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE515D09-16E1-4758-AA90-D3D12C1FC59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C016A4-18E7-4BD2-98B6-AFA4AFF45E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17156" uniqueCount="7396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17149" uniqueCount="7392">
   <si>
     <t>passNumber</t>
   </si>
@@ -22196,25 +22196,13 @@
   </si>
   <si>
     <t>CHAFKAR CHOWK</t>
-  </si>
-  <si>
-    <t>PP20260714001715</t>
-  </si>
-  <si>
-    <t>LAV KUSH BIND</t>
-  </si>
-  <si>
-    <t>CHACKAN CHOWK</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -22227,18 +22215,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -22276,7 +22252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -22284,10 +22260,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22591,7 +22563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1717"/>
+  <dimension ref="A1:J1716"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -77496,40 +77468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1717" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1717" t="s">
-        <v>7392</v>
-      </c>
-      <c r="B1717" s="4">
-        <v>232678</v>
-      </c>
-      <c r="C1717" s="5" t="s">
-        <v>7393</v>
-      </c>
-      <c r="D1717" s="5" t="s">
-        <v>7393</v>
-      </c>
-      <c r="E1717">
-        <v>7080904965</v>
-      </c>
-      <c r="F1717" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1717">
-        <v>33</v>
-      </c>
-      <c r="H1717" t="s">
-        <v>7394</v>
-      </c>
-      <c r="I1717" t="s">
-        <v>7395</v>
-      </c>
-      <c r="J1717" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/passes.xlsx
+++ b/passes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C016A4-18E7-4BD2-98B6-AFA4AFF45E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4AC27-4FD5-4D5E-8004-DEE2F93CBFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47772,10 +47772,10 @@
         <v>14</v>
       </c>
       <c r="G788" s="2" t="s">
-        <v>53</v>
+        <v>465</v>
       </c>
       <c r="H788" t="s">
-        <v>2512</v>
+        <v>3637</v>
       </c>
       <c r="I788" t="s">
         <v>39</v>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -11374,6 +11374,9 @@
     <t>Nageshvr vidyalay chikhali</t>
   </si>
   <si>
+    <t>TALAWADE CHOWK</t>
+  </si>
+  <si>
     <t>CHAKAN  CHOWK</t>
   </si>
   <si>
@@ -11393,9 +11396,6 @@
   </si>
   <si>
     <t>ABHILASHA PARK</t>
-  </si>
-  <si>
-    <t>TALAWADE CHOWK</t>
   </si>
   <si>
     <t>TRIVENINAGR CHOWK</t>
@@ -37354,10 +37354,10 @@
         <v>3487</v>
       </c>
       <c r="G788">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H788" t="s">
-        <v>3714</v>
+        <v>3786</v>
       </c>
       <c r="I788" t="s">
         <v>3937</v>
@@ -37453,7 +37453,7 @@
         <v>33</v>
       </c>
       <c r="H791" t="s">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="I791" t="s">
         <v>3937</v>
@@ -37741,7 +37741,7 @@
         <v>33</v>
       </c>
       <c r="H800" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="I800" t="s">
         <v>3937</v>
@@ -37773,7 +37773,7 @@
         <v>33</v>
       </c>
       <c r="H801" t="s">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="I801" t="s">
         <v>3937</v>
@@ -37805,7 +37805,7 @@
         <v>35</v>
       </c>
       <c r="H802" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="I802" t="s">
         <v>3937</v>
@@ -37837,7 +37837,7 @@
         <v>35</v>
       </c>
       <c r="H803" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="I803" t="s">
         <v>3937</v>
@@ -37901,7 +37901,7 @@
         <v>18</v>
       </c>
       <c r="H805" t="s">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="I805" t="s">
         <v>3937</v>
@@ -37933,7 +37933,7 @@
         <v>18</v>
       </c>
       <c r="H806" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I806" t="s">
         <v>3937</v>
@@ -38061,7 +38061,7 @@
         <v>14</v>
       </c>
       <c r="H810" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I810" t="s">
         <v>3937</v>
@@ -38157,7 +38157,7 @@
         <v>15</v>
       </c>
       <c r="H813" t="s">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="I813" t="s">
         <v>3937</v>
@@ -38253,7 +38253,7 @@
         <v>28</v>
       </c>
       <c r="H816" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I816" t="s">
         <v>3937</v>
@@ -39949,7 +39949,7 @@
         <v>14</v>
       </c>
       <c r="H869" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I869" t="s">
         <v>3937</v>
@@ -41549,7 +41549,7 @@
         <v>34</v>
       </c>
       <c r="H919" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="I919" t="s">
         <v>3937</v>
@@ -41581,7 +41581,7 @@
         <v>10</v>
       </c>
       <c r="H920" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I920" t="s">
         <v>3937</v>
@@ -41741,7 +41741,7 @@
         <v>34</v>
       </c>
       <c r="H925" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="I925" t="s">
         <v>3937</v>
@@ -43725,7 +43725,7 @@
         <v>19</v>
       </c>
       <c r="H987" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I987" t="s">
         <v>3937</v>
@@ -49578,7 +49578,7 @@
         <v>19</v>
       </c>
       <c r="H1170" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I1170" t="s">
         <v>3937</v>
@@ -49674,7 +49674,7 @@
         <v>19</v>
       </c>
       <c r="H1173" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I1173" t="s">
         <v>3937</v>
@@ -50523,7 +50523,7 @@
         <v>14</v>
       </c>
       <c r="H1200" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I1200" t="s">
         <v>3937</v>
@@ -51387,7 +51387,7 @@
         <v>14</v>
       </c>
       <c r="H1227" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I1227" t="s">
         <v>3937</v>
@@ -52955,7 +52955,7 @@
         <v>34</v>
       </c>
       <c r="H1276" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I1276" t="s">
         <v>3937</v>
@@ -53115,7 +53115,7 @@
         <v>19</v>
       </c>
       <c r="H1281" t="s">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="I1281" t="s">
         <v>3937</v>
@@ -53499,7 +53499,7 @@
         <v>14</v>
       </c>
       <c r="H1293" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="I1293" t="s">
         <v>3937</v>
@@ -62171,7 +62171,7 @@
         <v>33</v>
       </c>
       <c r="H1564" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="I1564" t="s">
         <v>3937</v>
@@ -62267,7 +62267,7 @@
         <v>33</v>
       </c>
       <c r="H1567" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="I1567" t="s">
         <v>3937</v>
@@ -62331,7 +62331,7 @@
         <v>33</v>
       </c>
       <c r="H1569" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="I1569" t="s">
         <v>3937</v>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -11837,8 +11837,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -11854,7 +11862,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -11862,12 +11870,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12166,34 +12192,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/passes.xlsx
+++ b/passes.xlsx
@@ -11374,28 +11374,28 @@
     <t>Nageshvr vidyalay chikhali</t>
   </si>
   <si>
+    <t>CHAKAN  CHOWK</t>
+  </si>
+  <si>
+    <t>RANUBAI MALA</t>
+  </si>
+  <si>
+    <t>AROGYAM HOSPITAL</t>
+  </si>
+  <si>
+    <t>AKURDI GATE</t>
+  </si>
+  <si>
+    <t>Canbay Chowk Dehugaon</t>
+  </si>
+  <si>
+    <t>PMT CHOWK BHOSARI</t>
+  </si>
+  <si>
+    <t>ABHILASHA PARK</t>
+  </si>
+  <si>
     <t>TALAWADE CHOWK</t>
-  </si>
-  <si>
-    <t>CHAKAN  CHOWK</t>
-  </si>
-  <si>
-    <t>RANUBAI MALA</t>
-  </si>
-  <si>
-    <t>AROGYAM HOSPITAL</t>
-  </si>
-  <si>
-    <t>AKURDI GATE</t>
-  </si>
-  <si>
-    <t>Canbay Chowk Dehugaon</t>
-  </si>
-  <si>
-    <t>PMT CHOWK BHOSARI</t>
-  </si>
-  <si>
-    <t>ABHILASHA PARK</t>
   </si>
   <si>
     <t>TRIVENINAGR CHOWK</t>
@@ -11837,16 +11837,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -11862,7 +11854,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -11870,30 +11862,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12192,34 +12166,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -37380,10 +37354,10 @@
         <v>3487</v>
       </c>
       <c r="G788">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H788" t="s">
-        <v>3786</v>
+        <v>3714</v>
       </c>
       <c r="I788" t="s">
         <v>3937</v>
@@ -37479,7 +37453,7 @@
         <v>33</v>
       </c>
       <c r="H791" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="I791" t="s">
         <v>3937</v>
@@ -37767,7 +37741,7 @@
         <v>33</v>
       </c>
       <c r="H800" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="I800" t="s">
         <v>3937</v>
@@ -37799,7 +37773,7 @@
         <v>33</v>
       </c>
       <c r="H801" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="I801" t="s">
         <v>3937</v>
@@ -37831,7 +37805,7 @@
         <v>35</v>
       </c>
       <c r="H802" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="I802" t="s">
         <v>3937</v>
@@ -37863,7 +37837,7 @@
         <v>35</v>
       </c>
       <c r="H803" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="I803" t="s">
         <v>3937</v>
@@ -37927,7 +37901,7 @@
         <v>18</v>
       </c>
       <c r="H805" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="I805" t="s">
         <v>3937</v>
@@ -37959,7 +37933,7 @@
         <v>18</v>
       </c>
       <c r="H806" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I806" t="s">
         <v>3937</v>
@@ -38087,7 +38061,7 @@
         <v>14</v>
       </c>
       <c r="H810" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I810" t="s">
         <v>3937</v>
@@ -38183,7 +38157,7 @@
         <v>15</v>
       </c>
       <c r="H813" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="I813" t="s">
         <v>3937</v>
@@ -38279,7 +38253,7 @@
         <v>28</v>
       </c>
       <c r="H816" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I816" t="s">
         <v>3937</v>
@@ -39975,7 +39949,7 @@
         <v>14</v>
       </c>
       <c r="H869" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I869" t="s">
         <v>3937</v>
@@ -41575,7 +41549,7 @@
         <v>34</v>
       </c>
       <c r="H919" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="I919" t="s">
         <v>3937</v>
@@ -41607,7 +41581,7 @@
         <v>10</v>
       </c>
       <c r="H920" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I920" t="s">
         <v>3937</v>
@@ -41767,7 +41741,7 @@
         <v>34</v>
       </c>
       <c r="H925" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="I925" t="s">
         <v>3937</v>
@@ -43751,7 +43725,7 @@
         <v>19</v>
       </c>
       <c r="H987" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I987" t="s">
         <v>3937</v>
@@ -49604,7 +49578,7 @@
         <v>19</v>
       </c>
       <c r="H1170" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I1170" t="s">
         <v>3937</v>
@@ -49700,7 +49674,7 @@
         <v>19</v>
       </c>
       <c r="H1173" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I1173" t="s">
         <v>3937</v>
@@ -50549,7 +50523,7 @@
         <v>14</v>
       </c>
       <c r="H1200" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I1200" t="s">
         <v>3937</v>
@@ -51413,7 +51387,7 @@
         <v>14</v>
       </c>
       <c r="H1227" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I1227" t="s">
         <v>3937</v>
@@ -52981,7 +52955,7 @@
         <v>34</v>
       </c>
       <c r="H1276" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I1276" t="s">
         <v>3937</v>
@@ -53141,7 +53115,7 @@
         <v>19</v>
       </c>
       <c r="H1281" t="s">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="I1281" t="s">
         <v>3937</v>
@@ -53525,7 +53499,7 @@
         <v>14</v>
       </c>
       <c r="H1293" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="I1293" t="s">
         <v>3937</v>
@@ -62197,7 +62171,7 @@
         <v>33</v>
       </c>
       <c r="H1564" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="I1564" t="s">
         <v>3937</v>
@@ -62293,7 +62267,7 @@
         <v>33</v>
       </c>
       <c r="H1567" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="I1567" t="s">
         <v>3937</v>
@@ -62357,7 +62331,7 @@
         <v>33</v>
       </c>
       <c r="H1569" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="I1569" t="s">
         <v>3937</v>
